--- a/data_static/piscinas/piscinas.xlsx
+++ b/data_static/piscinas/piscinas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c476c95a5a05174c/OD/LOFEC - TAPIOCA/RCP/Aditivo/Praia segura/APP/praia_segura/data_static/piscinas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\piscinas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B94B9EB-99FC-4471-AEB7-F295CF62D100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF045D6-1678-421A-AA99-92ACF5BE416D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8CF4131F-23A0-46B3-B454-BFAA20E5CCB4}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{8CF4131F-23A0-46B3-B454-BFAA20E5CCB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -171,18 +171,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -197,9 +191,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -544,52 +537,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -624,11 +617,11 @@
       <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>3</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
         <v>2</v>
@@ -668,11 +661,11 @@
       <c r="J3" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="s">
         <v>2</v>
@@ -712,11 +705,11 @@
       <c r="J4" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="s">
         <v>3</v>
@@ -756,11 +749,11 @@
       <c r="J5" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" t="s">
         <v>2</v>
@@ -800,11 +793,11 @@
       <c r="J6" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="s">
         <v>2</v>
@@ -847,11 +840,11 @@
       <c r="J7" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>3</v>
       </c>
       <c r="L7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" t="s">
         <v>2</v>
@@ -891,11 +884,11 @@
       <c r="J8" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>3</v>
       </c>
       <c r="L8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="s">
         <v>2</v>
@@ -935,11 +928,11 @@
       <c r="J9" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="s">
         <v>2</v>
@@ -979,11 +972,11 @@
       <c r="J10" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="s">
         <v>2</v>

--- a/data_static/piscinas/piscinas.xlsx
+++ b/data_static/piscinas/piscinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\piscinas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF045D6-1678-421A-AA99-92ACF5BE416D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550CAC6B-D3A0-4F92-8E1F-FD90ADC050FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{8CF4131F-23A0-46B3-B454-BFAA20E5CCB4}"/>
+    <workbookView xWindow="9510" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{8CF4131F-23A0-46B3-B454-BFAA20E5CCB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="46">
   <si>
     <t>ID_0001</t>
   </si>
@@ -80,9 +80,6 @@
     <t xml:space="preserve">sim </t>
   </si>
   <si>
-    <t>Praia sem barreiras (lat: -8.12171; lon: -34.895544)</t>
-  </si>
-  <si>
     <t>ID_0019</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>Atlante Plaza</t>
   </si>
   <si>
-    <t>Correntes de retorno</t>
-  </si>
-  <si>
     <t>ID_SETOR</t>
   </si>
   <si>
@@ -152,20 +146,66 @@
     <t>ACESSIBILIDADE</t>
   </si>
   <si>
-    <t>CLASS_BALNEABILIDADE</t>
-  </si>
-  <si>
     <t>OBSERVACAO</t>
+  </si>
+  <si>
+    <t>ENRONCAMENTO</t>
+  </si>
+  <si>
+    <t>COD_CPRH_BALNEABILIDADE</t>
+  </si>
+  <si>
+    <t>DIST_ESTACAO_CPRH_KM</t>
+  </si>
+  <si>
+    <t>REC-80</t>
+  </si>
+  <si>
+    <t>Piscinas naturais em maré baixa. Não arrisque durante maré alta!</t>
+  </si>
+  <si>
+    <t>ID_0008</t>
+  </si>
+  <si>
+    <t>Pina 4</t>
+  </si>
+  <si>
+    <t>Piscina natural restrita com correntes de retorno. Banho não é indicado.</t>
+  </si>
+  <si>
+    <t>REC-50</t>
+  </si>
+  <si>
+    <t>REC-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -179,7 +219,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -187,20 +227,78 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -530,67 +628,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6CEEDC-DE51-4D66-8F27-2BB9D4916580}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="49.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="18" max="18" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2">
@@ -614,8 +720,8 @@
       <c r="I2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>3</v>
+      <c r="J2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="K2" t="s">
         <v>3</v>
@@ -629,12 +735,24 @@
       <c r="N2" t="s">
         <v>2</v>
       </c>
+      <c r="O2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2">
+        <v>1.4269000000000001</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3">
@@ -656,9 +774,9 @@
         <v>-34.879660000000001</v>
       </c>
       <c r="I3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K3" t="s">
@@ -671,14 +789,26 @@
         <v>2</v>
       </c>
       <c r="N3" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3">
+        <v>0.26050000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4">
@@ -700,9 +830,9 @@
         <v>-34.880653000000002</v>
       </c>
       <c r="I4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K4" t="s">
@@ -717,278 +847,428 @@
       <c r="N4" t="s">
         <v>2</v>
       </c>
+      <c r="O4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4">
+        <v>0.15989999999999999</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>-8.0962560000000003</v>
+      </c>
+      <c r="D5">
+        <v>-34.881883000000002</v>
+      </c>
+      <c r="E5">
+        <v>-8.0988450000000007</v>
+      </c>
+      <c r="F5">
+        <v>-34.882792000000002</v>
+      </c>
+      <c r="G5">
+        <v>-8.0973220000000001</v>
+      </c>
+      <c r="H5">
+        <v>-34.882250999999997</v>
+      </c>
+      <c r="I5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>2</v>
+      </c>
+      <c r="P5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5">
+        <v>0.69530000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>-8.1158020000000004</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>-34.891592000000003</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>-8.1181280000000005</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>-34.893061000000003</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>-8.1169119999999992</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>-34.892294</v>
       </c>
-      <c r="I5" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2</v>
-      </c>
-      <c r="N5" t="s">
-        <v>2</v>
+      <c r="I6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6">
+        <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>-8.1204190000000001</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>-34.894509999999997</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>-8.1228390000000008</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>-34.895823999999998</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>-8.1215430000000008</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>-34.895113000000002</v>
       </c>
-      <c r="I6" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
         <v>12</v>
       </c>
-      <c r="K6" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2</v>
-      </c>
-      <c r="N6" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="L7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7">
+        <v>0.77459999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>-8.1228390000000008</v>
+      </c>
+      <c r="D8">
+        <v>-34.895823999999998</v>
+      </c>
+      <c r="E8">
+        <v>-8.1255620000000004</v>
+      </c>
+      <c r="F8">
+        <v>-34.896779000000002</v>
+      </c>
+      <c r="G8">
+        <v>-8.1241839999999996</v>
+      </c>
+      <c r="H8">
+        <v>-34.896284000000001</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8">
+        <v>1.0947</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
-        <v>-8.1228390000000008</v>
-      </c>
-      <c r="D7">
-        <v>-34.895823999999998</v>
-      </c>
-      <c r="E7">
-        <v>-8.1255620000000004</v>
-      </c>
-      <c r="F7">
-        <v>-34.896779000000002</v>
-      </c>
-      <c r="G7">
-        <v>-8.1241839999999996</v>
-      </c>
-      <c r="H7">
-        <v>-34.896284000000001</v>
-      </c>
-      <c r="I7" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" t="s">
-        <v>2</v>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>-8.1306270000000005</v>
+      </c>
+      <c r="D9">
+        <v>-34.898820999999998</v>
+      </c>
+      <c r="E9">
+        <v>-8.1331129999999998</v>
+      </c>
+      <c r="F9">
+        <v>-34.899934000000002</v>
+      </c>
+      <c r="G9">
+        <v>-8.1317559999999993</v>
+      </c>
+      <c r="H9">
+        <v>-34.899334000000003</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9">
+        <v>1.9992000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="C8">
-        <v>-8.1306270000000005</v>
-      </c>
-      <c r="D8">
-        <v>-34.898820999999998</v>
-      </c>
-      <c r="E8">
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
         <v>-8.1331129999999998</v>
       </c>
-      <c r="F8">
+      <c r="D10">
         <v>-34.899934000000002</v>
       </c>
-      <c r="G8">
-        <v>-8.1317559999999993</v>
-      </c>
-      <c r="H8">
-        <v>-34.899334000000003</v>
-      </c>
-      <c r="I8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" t="s">
-        <v>2</v>
-      </c>
-      <c r="N8" t="s">
-        <v>2</v>
+      <c r="E10">
+        <v>-8.1356350000000006</v>
+      </c>
+      <c r="F10">
+        <v>-34.900987999999998</v>
+      </c>
+      <c r="G10">
+        <v>-8.1342630000000007</v>
+      </c>
+      <c r="H10">
+        <v>-34.900418000000002</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" t="s">
+        <v>2</v>
+      </c>
+      <c r="N10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R10">
+        <v>1.8567</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="C9">
-        <v>-8.1331129999999998</v>
-      </c>
-      <c r="D9">
-        <v>-34.899934000000002</v>
-      </c>
-      <c r="E9">
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
         <v>-8.1356350000000006</v>
       </c>
-      <c r="F9">
+      <c r="D11">
         <v>-34.900987999999998</v>
       </c>
-      <c r="G9">
-        <v>-8.1342630000000007</v>
-      </c>
-      <c r="H9">
-        <v>-34.900418000000002</v>
-      </c>
-      <c r="I9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" t="s">
-        <v>2</v>
-      </c>
-      <c r="N9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10">
-        <v>-8.1356350000000006</v>
-      </c>
-      <c r="D10">
-        <v>-34.900987999999998</v>
-      </c>
-      <c r="E10">
+      <c r="E11">
         <v>-8.1382169999999991</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>-34.901840999999997</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>-8.1368919999999996</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <v>-34.901387999999997</v>
       </c>
-      <c r="I10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" t="s">
-        <v>2</v>
-      </c>
-      <c r="N10" t="s">
-        <v>2</v>
-      </c>
-      <c r="P10" t="s">
-        <v>22</v>
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11">
+        <v>1.5459000000000001</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:J11">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:M11">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>